--- a/Student_Performance_Data (version 1).xlsb.xlsx
+++ b/Student_Performance_Data (version 1).xlsb.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\New folder (2)\Excel-Basics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2BD7B3-7E8C-4D90-9376-8E3EF46BDF11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{829F311B-A82E-42B1-AD49-150B4FDA85B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11048" uniqueCount="2864">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11051" uniqueCount="2867">
   <si>
     <t>Student ID</t>
   </si>
@@ -8650,6 +8650,15 @@
   </si>
   <si>
     <t>Number of Poor Students</t>
+  </si>
+  <si>
+    <t>here</t>
+  </si>
+  <si>
+    <t>s1008</t>
+  </si>
+  <si>
+    <t>s1000</t>
   </si>
 </sst>
 </file>
@@ -10005,7 +10014,7 @@
         <v>2850</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -10064,8 +10073,11 @@
       <c r="U17" s="3" t="s">
         <v>2025</v>
       </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z17" t="s">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -10123,8 +10135,11 @@
       <c r="U18" s="3" t="s">
         <v>2026</v>
       </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z18" t="s">
+        <v>2865</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -10183,7 +10198,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -10242,8 +10257,12 @@
       <c r="U20" s="3" t="s">
         <v>2028</v>
       </c>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="X20">
+        <f>VLOOKUP(Z18,A1:P1001,11,FALSE)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -10302,7 +10321,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -10361,7 +10380,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -10420,7 +10439,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -10479,7 +10498,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -10538,7 +10557,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>35</v>
       </c>
@@ -10597,7 +10616,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>36</v>
       </c>
@@ -10651,7 +10670,7 @@
       </c>
       <c r="T27" s="1"/>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>37</v>
       </c>
@@ -10704,7 +10723,7 @@
         <v>Fail</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>38</v>
       </c>
@@ -10758,7 +10777,7 @@
       </c>
       <c r="Y29" s="5"/>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>39</v>
       </c>
@@ -10811,7 +10830,7 @@
         <v>Good</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -10864,7 +10883,7 @@
         <v>Very Good</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>41</v>
       </c>
@@ -62281,56 +62300,48 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B08BE37-9E8D-4CEA-A8A7-C4E65CA85FBE}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="B5:I11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1">
-        <f>Sheet2!A2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <f>Sheet2!A3*1</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="2">
-        <v>47119</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="2">
-        <v>51136</v>
-      </c>
-      <c r="E10" s="2">
-        <f>MIN(B9:B11)</f>
-        <v>46753</v>
-      </c>
-      <c r="G10">
-        <f>E10-E11</f>
-        <v>-4383</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="2">
-        <v>46753</v>
-      </c>
-      <c r="E11" s="2">
-        <f>MAX(B9:B11)</f>
-        <v>51136</v>
-      </c>
-      <c r="G11">
-        <f>E11-E10</f>
-        <v>4383</v>
-      </c>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="I5" t="s">
+        <v>2866</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E8" t="str" cm="1">
+        <f t="array" ref="E8:I8">_xlfn.XLOOKUP(I5,Sheet1!A:A,_xlfn.CHOOSECOLS(Sheet1!A:P,2,9,10,11,16),"Not Found",0)</f>
+        <v>Karen Alvarado</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Science</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Final</v>
+      </c>
+      <c r="H8">
+        <v>94</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Excellent</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="2"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B11" s="2"/>
+      <c r="E11" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Student_Performance_Data (version 1).xlsb.xlsx
+++ b/Student_Performance_Data (version 1).xlsb.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\New folder (2)\Excel-Basics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{829F311B-A82E-42B1-AD49-150B4FDA85B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17B4EAC-6D3A-482C-B7DE-F74A609BBF02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$1001</definedName>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -58,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11051" uniqueCount="2867">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11059" uniqueCount="2875">
   <si>
     <t>Student ID</t>
   </si>
@@ -8659,13 +8660,37 @@
   </si>
   <si>
     <t>s1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter Student Id </t>
+  </si>
+  <si>
+    <t>Studen Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name </t>
+  </si>
+  <si>
+    <t xml:space="preserve">School </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exam Type </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student level </t>
+  </si>
+  <si>
+    <t>s1016</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8681,8 +8706,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8701,6 +8733,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -8714,7 +8752,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -8727,11 +8765,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -62346,4 +62397,91 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3271FC-9C2B-4CD7-A8A4-2A50EFD7B70C}">
+  <dimension ref="F3:K8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.140625" customWidth="1"/>
+    <col min="8" max="8" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="6:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="H3" s="9" t="s">
+        <v>2867</v>
+      </c>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+    </row>
+    <row r="5" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="H5" s="10" t="s">
+        <v>2874</v>
+      </c>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+    </row>
+    <row r="7" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="F7" s="8" t="s">
+        <v>2868</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>2869</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>2870</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>2872</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>2871</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>2873</v>
+      </c>
+    </row>
+    <row r="8" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="F8" t="str" cm="1">
+        <f t="array" ref="F8:K8">_xlfn.XLOOKUP(H5,Sheet1!A:A,_xlfn.CHOOSECOLS(Sheet1!A:P,1,2,7,10,11,16),"Not Found",0)</f>
+        <v>S1016</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Danielle Campos</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Brooklyn Technical High School</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Final</v>
+      </c>
+      <c r="J8">
+        <v>96</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Excellent</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="H5:J5"/>
+  </mergeCells>
+  <conditionalFormatting sqref="F8:K8">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$F8="Excellent"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="stop " error="enter valid id" promptTitle="select id" sqref="H5:J5" xr:uid="{1CDEEB68-CE67-4A05-9BFD-E14634108261}">
+      <formula1>6</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Student_Performance_Data (version 1).xlsb.xlsx
+++ b/Student_Performance_Data (version 1).xlsb.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\New folder (2)\Excel-Basics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17B4EAC-6D3A-482C-B7DE-F74A609BBF02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E713D1-3667-4145-A9A0-57CC765AA69B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
+    <sheet name="Practice" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$1001</definedName>
@@ -59,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11059" uniqueCount="2875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11064" uniqueCount="2872">
   <si>
     <t>Student ID</t>
   </si>
@@ -8659,38 +8658,29 @@
     <t>s1008</t>
   </si>
   <si>
-    <t>s1000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter Student Id </t>
-  </si>
-  <si>
-    <t>Studen Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name </t>
-  </si>
-  <si>
-    <t xml:space="preserve">School </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Score </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exam Type </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student level </t>
-  </si>
-  <si>
-    <t>s1016</t>
+    <t>Student Id</t>
+  </si>
+  <si>
+    <t>Student Level</t>
+  </si>
+  <si>
+    <t>Enter Student ID</t>
+  </si>
+  <si>
+    <t>s1005</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>pass</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8707,14 +8697,37 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8735,12 +8748,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -8748,14 +8767,153 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -8765,21 +8923,87 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="6">
     <dxf>
       <font>
-        <color rgb="FF0070C0"/>
+        <color rgb="FF00B0F0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B0F0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B0F0"/>
       </font>
     </dxf>
   </dxfs>
@@ -9103,52 +9327,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>2846</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>2847</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="6" t="s">
         <v>2852</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="6" t="s">
         <v>2855</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="6" t="s">
         <v>2858</v>
       </c>
     </row>
@@ -9434,17 +9658,17 @@
         <f t="array" ref="P6">_xlfn.IFS(K6&gt;90,"Excellent",K6&gt;80,"Very Good",K6&gt;70,"Good",K6&gt;=50,"Poor",K6&lt;50,"Fail")</f>
         <v>Good</v>
       </c>
-      <c r="R6" s="4" t="s">
+      <c r="R6" s="3" t="s">
         <v>2848</v>
       </c>
-      <c r="S6" s="4">
+      <c r="S6" s="3">
         <f>MIN(F2:F1001)</f>
         <v>14</v>
       </c>
-      <c r="U6" s="4" t="s">
+      <c r="U6" t="s">
         <v>2853</v>
       </c>
-      <c r="V6" s="4">
+      <c r="V6" s="3">
         <f>COUNTIF(N2:N1001,"Pass")</f>
         <v>501</v>
       </c>
@@ -9501,17 +9725,17 @@
         <f t="array" ref="P7">_xlfn.IFS(K7&gt;90,"Excellent",K7&gt;80,"Very Good",K7&gt;70,"Good",K7&gt;=50,"Poor",K7&lt;50,"Fail")</f>
         <v>Fail</v>
       </c>
-      <c r="R7" s="4" t="s">
+      <c r="R7" s="3" t="s">
         <v>2849</v>
       </c>
-      <c r="S7" s="4">
+      <c r="S7" s="3">
         <f>MAX(F2:F1001)</f>
         <v>18</v>
       </c>
-      <c r="U7" s="4" t="s">
+      <c r="U7" s="3" t="s">
         <v>2854</v>
       </c>
-      <c r="V7" s="4">
+      <c r="V7" s="3">
         <f>COUNTIF(N2:N1001,"Fail")</f>
         <v>499</v>
       </c>
@@ -9568,12 +9792,8 @@
         <f t="array" ref="P8">_xlfn.IFS(K8&gt;90,"Excellent",K8&gt;80,"Very Good",K8&gt;70,"Good",K8&gt;=50,"Poor",K8&lt;50,"Fail")</f>
         <v>Very Good</v>
       </c>
-      <c r="X8" s="4" t="s">
-        <v>2007</v>
-      </c>
-      <c r="Y8" s="4" t="s">
-        <v>2008</v>
-      </c>
+      <c r="X8" s="3"/>
+      <c r="Y8" s="3"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -9627,28 +9847,22 @@
         <f t="array" ref="P9">_xlfn.IFS(K9&gt;90,"Excellent",K9&gt;80,"Very Good",K9&gt;70,"Good",K9&gt;=50,"Poor",K9&lt;50,"Fail")</f>
         <v>Fail</v>
       </c>
-      <c r="R9" s="4" t="s">
+      <c r="R9" s="3" t="s">
         <v>2856</v>
       </c>
-      <c r="S9" s="4">
+      <c r="S9" s="3">
         <f>COUNTIF(O2:O1001,"Adult")</f>
         <v>208</v>
       </c>
-      <c r="U9" s="4" t="s">
+      <c r="U9" s="3" t="s">
         <v>2859</v>
       </c>
-      <c r="V9" s="4">
+      <c r="V9" s="3">
         <f>COUNTIF(P2:P1001,"Excellent")</f>
         <v>110</v>
       </c>
-      <c r="X9" s="4">
-        <f>COUNTIFS(E2:E1001,E2,P2:P1001,P2)</f>
-        <v>60</v>
-      </c>
-      <c r="Y9" s="4">
-        <f>V9-X9</f>
-        <v>50</v>
-      </c>
+      <c r="X9" s="3"/>
+      <c r="Y9" s="3"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -9702,17 +9916,17 @@
         <f t="array" ref="P10">_xlfn.IFS(K10&gt;90,"Excellent",K10&gt;80,"Very Good",K10&gt;70,"Good",K10&gt;=50,"Poor",K10&lt;50,"Fail")</f>
         <v>Fail</v>
       </c>
-      <c r="R10" s="4" t="s">
+      <c r="R10" s="3" t="s">
         <v>2857</v>
       </c>
-      <c r="S10" s="4">
+      <c r="S10" s="3">
         <f>COUNTIF(O2:O1001,"UnderAge")</f>
         <v>792</v>
       </c>
-      <c r="U10" s="4" t="s">
+      <c r="U10" s="3" t="s">
         <v>2860</v>
       </c>
-      <c r="V10" s="4">
+      <c r="V10" s="3">
         <f>COUNTIF(P2:P1001,"Very Good")</f>
         <v>103</v>
       </c>
@@ -9769,10 +9983,10 @@
         <f t="array" ref="P11">_xlfn.IFS(K11&gt;90,"Excellent",K11&gt;80,"Very Good",K11&gt;70,"Good",K11&gt;=50,"Poor",K11&lt;50,"Fail")</f>
         <v>Poor</v>
       </c>
-      <c r="U11" s="4" t="s">
+      <c r="U11" s="3" t="s">
         <v>2861</v>
       </c>
-      <c r="V11" s="4">
+      <c r="V11" s="3">
         <f>COUNTIF(P2:P1001,"Good")</f>
         <v>85</v>
       </c>
@@ -9829,10 +10043,10 @@
         <f t="array" ref="P12">_xlfn.IFS(K12&gt;90,"Excellent",K12&gt;80,"Very Good",K12&gt;70,"Good",K12&gt;=50,"Poor",K12&lt;50,"Fail")</f>
         <v>Fail</v>
       </c>
-      <c r="U12" s="4" t="s">
+      <c r="U12" s="3" t="s">
         <v>2862</v>
       </c>
-      <c r="V12" s="4">
+      <c r="V12" s="3">
         <f>COUNTIF(P2:P1001,"Fail")</f>
         <v>499</v>
       </c>
@@ -9889,10 +10103,10 @@
         <f t="array" ref="P13">_xlfn.IFS(K13&gt;90,"Excellent",K13&gt;80,"Very Good",K13&gt;70,"Good",K13&gt;=50,"Poor",K13&lt;50,"Fail")</f>
         <v>Very Good</v>
       </c>
-      <c r="U13" s="4" t="s">
+      <c r="U13" s="3" t="s">
         <v>2863</v>
       </c>
-      <c r="V13" s="4">
+      <c r="V13" s="3">
         <f>COUNTIF(P2:P1001,P17)</f>
         <v>203</v>
       </c>
@@ -10002,7 +10216,7 @@
         <f t="array" ref="P15">_xlfn.IFS(K15&gt;90,"Excellent",K15&gt;80,"Very Good",K15&gt;70,"Good",K15&gt;=50,"Poor",K15&lt;50,"Fail")</f>
         <v>Very Good</v>
       </c>
-      <c r="U15" s="6" t="s">
+      <c r="U15" s="5" t="s">
         <v>2851</v>
       </c>
     </row>
@@ -10058,10 +10272,10 @@
         <f t="array" ref="P16">_xlfn.IFS(K16&gt;90,"Excellent",K16&gt;80,"Very Good",K16&gt;70,"Good",K16&gt;=50,"Poor",K16&lt;50,"Fail")</f>
         <v>Fail</v>
       </c>
-      <c r="R16" s="4" t="s">
+      <c r="R16" s="3" t="s">
         <v>2850</v>
       </c>
-      <c r="U16" s="4" t="s">
+      <c r="U16" s="3" t="s">
         <v>2850</v>
       </c>
     </row>
@@ -10117,11 +10331,11 @@
         <f t="array" ref="P17">_xlfn.IFS(K17&gt;90,"Excellent",K17&gt;80,"Very Good",K17&gt;70,"Good",K17&gt;=50,"Poor",K17&lt;50,"Fail")</f>
         <v>Poor</v>
       </c>
-      <c r="R17" s="3" t="str" cm="1">
+      <c r="R17" s="2" t="str" cm="1">
         <f t="array" ref="R17:R26">_xlfn.UNIQUE(L2:L1001)</f>
         <v>Kevin Carson</v>
       </c>
-      <c r="U17" s="3" t="s">
+      <c r="U17" s="2" t="s">
         <v>2025</v>
       </c>
       <c r="Z17" t="s">
@@ -10180,10 +10394,10 @@
         <f t="array" ref="P18">_xlfn.IFS(K18&gt;90,"Excellent",K18&gt;80,"Very Good",K18&gt;70,"Good",K18&gt;=50,"Poor",K18&lt;50,"Fail")</f>
         <v>Excellent</v>
       </c>
-      <c r="R18" s="3" t="str">
+      <c r="R18" s="2" t="str">
         <v>Kathryn Paul</v>
       </c>
-      <c r="U18" s="3" t="s">
+      <c r="U18" s="2" t="s">
         <v>2026</v>
       </c>
       <c r="Z18" t="s">
@@ -10242,10 +10456,10 @@
         <f t="array" ref="P19">_xlfn.IFS(K19&gt;90,"Excellent",K19&gt;80,"Very Good",K19&gt;70,"Good",K19&gt;=50,"Poor",K19&lt;50,"Fail")</f>
         <v>Fail</v>
       </c>
-      <c r="R19" s="3" t="str">
+      <c r="R19" s="2" t="str">
         <v>Juan Reynolds</v>
       </c>
-      <c r="U19" s="3" t="s">
+      <c r="U19" s="2" t="s">
         <v>2027</v>
       </c>
     </row>
@@ -10301,11 +10515,11 @@
         <f t="array" ref="P20">_xlfn.IFS(K20&gt;90,"Excellent",K20&gt;80,"Very Good",K20&gt;70,"Good",K20&gt;=50,"Poor",K20&lt;50,"Fail")</f>
         <v>Fail</v>
       </c>
-      <c r="R20" s="3" t="str">
+      <c r="R20" s="2" t="str">
         <v>Scott Rodgers DDS</v>
       </c>
       <c r="T20" s="1"/>
-      <c r="U20" s="3" t="s">
+      <c r="U20" s="2" t="s">
         <v>2028</v>
       </c>
       <c r="X20">
@@ -10365,10 +10579,10 @@
         <f t="array" ref="P21">_xlfn.IFS(K21&gt;90,"Excellent",K21&gt;80,"Very Good",K21&gt;70,"Good",K21&gt;=50,"Poor",K21&lt;50,"Fail")</f>
         <v>Fail</v>
       </c>
-      <c r="R21" s="3" t="str">
+      <c r="R21" s="2" t="str">
         <v>Jeffrey Miller</v>
       </c>
-      <c r="U21" s="3" t="s">
+      <c r="U21" s="2" t="s">
         <v>2029</v>
       </c>
     </row>
@@ -10424,10 +10638,10 @@
         <f t="array" ref="P22">_xlfn.IFS(K22&gt;90,"Excellent",K22&gt;80,"Very Good",K22&gt;70,"Good",K22&gt;=50,"Poor",K22&lt;50,"Fail")</f>
         <v>Poor</v>
       </c>
-      <c r="R22" s="3" t="str">
+      <c r="R22" s="2" t="str">
         <v>Deborah Clark</v>
       </c>
-      <c r="U22" s="3" t="s">
+      <c r="U22" s="2" t="s">
         <v>2030</v>
       </c>
     </row>
@@ -10483,10 +10697,10 @@
         <f t="array" ref="P23">_xlfn.IFS(K23&gt;90,"Excellent",K23&gt;80,"Very Good",K23&gt;70,"Good",K23&gt;=50,"Poor",K23&lt;50,"Fail")</f>
         <v>Good</v>
       </c>
-      <c r="R23" s="3" t="str">
+      <c r="R23" s="2" t="str">
         <v>Curtis Norman</v>
       </c>
-      <c r="U23" s="3" t="s">
+      <c r="U23" s="2" t="s">
         <v>2031</v>
       </c>
     </row>
@@ -10542,10 +10756,10 @@
         <f t="array" ref="P24">_xlfn.IFS(K24&gt;90,"Excellent",K24&gt;80,"Very Good",K24&gt;70,"Good",K24&gt;=50,"Poor",K24&lt;50,"Fail")</f>
         <v>Fail</v>
       </c>
-      <c r="R24" s="3" t="str">
+      <c r="R24" s="2" t="str">
         <v>Nicole Hoffman</v>
       </c>
-      <c r="U24" s="3" t="s">
+      <c r="U24" s="2" t="s">
         <v>2032</v>
       </c>
     </row>
@@ -10601,10 +10815,10 @@
         <f t="array" ref="P25">_xlfn.IFS(K25&gt;90,"Excellent",K25&gt;80,"Very Good",K25&gt;70,"Good",K25&gt;=50,"Poor",K25&lt;50,"Fail")</f>
         <v>Good</v>
       </c>
-      <c r="R25" s="3" t="str">
+      <c r="R25" s="2" t="str">
         <v>Erik Grant</v>
       </c>
-      <c r="U25" s="3" t="s">
+      <c r="U25" s="2" t="s">
         <v>2033</v>
       </c>
     </row>
@@ -10660,14 +10874,14 @@
         <f t="array" ref="P26">_xlfn.IFS(K26&gt;90,"Excellent",K26&gt;80,"Very Good",K26&gt;70,"Good",K26&gt;=50,"Poor",K26&lt;50,"Fail")</f>
         <v>Excellent</v>
       </c>
-      <c r="R26" s="3" t="str">
+      <c r="R26" s="2" t="str">
         <v>Michael Gay</v>
       </c>
-      <c r="U26" s="3" t="s">
+      <c r="U26" s="2" t="s">
         <v>2034</v>
       </c>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>36</v>
       </c>
@@ -10711,7 +10925,7 @@
         <f t="shared" si="0"/>
         <v>Pass</v>
       </c>
-      <c r="O27" t="str">
+      <c r="O27" s="17" t="str">
         <f t="shared" si="1"/>
         <v>UnderAge</v>
       </c>
@@ -10826,7 +11040,7 @@
         <f t="array" ref="P29">_xlfn.IFS(K29&gt;90,"Excellent",K29&gt;80,"Very Good",K29&gt;70,"Good",K29&gt;=50,"Poor",K29&lt;50,"Fail")</f>
         <v>Poor</v>
       </c>
-      <c r="Y29" s="5"/>
+      <c r="Y29" s="4"/>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
@@ -62350,138 +62564,174 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B08BE37-9E8D-4CEA-A8A7-C4E65CA85FBE}">
-  <dimension ref="B5:I11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D84A2A18-36EB-4479-8A4B-7833D615430E}">
+  <dimension ref="B2:N12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" customWidth="1"/>
+    <col min="13" max="13" width="8.5703125" customWidth="1"/>
+    <col min="14" max="14" width="7.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="I5" t="s">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="K2" s="18" t="s">
+        <v>2859</v>
+      </c>
+      <c r="L2" s="18">
+        <f>COUNTIF(Sheet1!P:P,Sheet1!P2)</f>
+        <v>110</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>2008</v>
+      </c>
+      <c r="N2" s="19">
+        <f>COUNTIFS(Sheet1!E:E,Sheet1!E3,Sheet1!P:P,Sheet1!P2)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" ht="21" x14ac:dyDescent="0.35">
+      <c r="C3" s="8" t="s">
+        <v>2868</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="22"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C4" s="11" t="s">
+        <v>2869</v>
+      </c>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="13"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="19" t="s">
+        <v>2007</v>
+      </c>
+      <c r="N4" s="19">
+        <f>COUNTIFS(Sheet1!E:E,Sheet1!E2,Sheet1!P:P,Sheet1!P2)</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="14"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="16"/>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="L6" s="7"/>
+    </row>
+    <row r="7" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="9" t="s">
         <v>2866</v>
       </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="E8" t="str" cm="1">
-        <f t="array" ref="E8:I8">_xlfn.XLOOKUP(I5,Sheet1!A:A,_xlfn.CHOOSECOLS(Sheet1!A:P,2,9,10,11,16),"Not Found",0)</f>
-        <v>Karen Alvarado</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Science</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Final</v>
-      </c>
-      <c r="H8">
-        <v>94</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Excellent</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="2"/>
-      <c r="E11" s="2"/>
+      <c r="C7" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>2867</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="B8" s="10" t="str" cm="1">
+        <f t="array" ref="B8:H8">_xlfn.XLOOKUP(C4,Sheet1!A:A,_xlfn.CHOOSECOLS(Sheet1!A:P,1,2,5,8,9,10,16),"Not Found",0)</f>
+        <v>S1005</v>
+      </c>
+      <c r="C8" s="10" t="str">
+        <v>Andrew Torres</v>
+      </c>
+      <c r="D8" s="10" t="str">
+        <v>Male</v>
+      </c>
+      <c r="E8" s="10" t="str">
+        <v>Grade 11</v>
+      </c>
+      <c r="F8" s="10" t="str">
+        <v>Math</v>
+      </c>
+      <c r="G8" s="10" t="str">
+        <v>Midterm</v>
+      </c>
+      <c r="H8" s="10" t="str">
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="K9" s="24" t="s">
+        <v>2853</v>
+      </c>
+      <c r="L9" s="24">
+        <f>COUNTIF(Sheet1!N:N,Sheet1!N2)</f>
+        <v>501</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="K10" s="24" t="s">
+        <v>2854</v>
+      </c>
+      <c r="L10" s="24">
+        <f>COUNTIF(Sheet1!N:N,Sheet1!N3)</f>
+        <v>499</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>2870</v>
+      </c>
+      <c r="E11" s="26"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>2871</v>
+      </c>
+      <c r="E12" s="25"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3271FC-9C2B-4CD7-A8A4-2A50EFD7B70C}">
-  <dimension ref="F3:K8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="6" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.140625" customWidth="1"/>
-    <col min="8" max="8" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="6:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="H3" s="9" t="s">
-        <v>2867</v>
-      </c>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-    </row>
-    <row r="5" spans="6:11" x14ac:dyDescent="0.25">
-      <c r="H5" s="10" t="s">
-        <v>2874</v>
-      </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-    </row>
-    <row r="7" spans="6:11" x14ac:dyDescent="0.25">
-      <c r="F7" s="8" t="s">
-        <v>2868</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>2869</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>2870</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>2872</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>2871</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>2873</v>
-      </c>
-    </row>
-    <row r="8" spans="6:11" x14ac:dyDescent="0.25">
-      <c r="F8" t="str" cm="1">
-        <f t="array" ref="F8:K8">_xlfn.XLOOKUP(H5,Sheet1!A:A,_xlfn.CHOOSECOLS(Sheet1!A:P,1,2,7,10,11,16),"Not Found",0)</f>
-        <v>S1016</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Danielle Campos</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Brooklyn Technical High School</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Final</v>
-      </c>
-      <c r="J8">
-        <v>96</v>
-      </c>
-      <c r="K8" t="str">
-        <v>Excellent</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="H5:J5"/>
+  <mergeCells count="5">
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G5"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="L2:L4"/>
   </mergeCells>
-  <conditionalFormatting sqref="F8:K8">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$F8="Excellent"</formula>
+  <conditionalFormatting sqref="B8:H8">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$H8="Fail"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2">
+      <formula>"="</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>$H8="Excellent"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="stop " error="enter valid id" promptTitle="select id" sqref="H5:J5" xr:uid="{1CDEEB68-CE67-4A05-9BFD-E14634108261}">
-      <formula1>6</formula1>
-      <formula2>10</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>